--- a/documentation/parts-list.xlsx
+++ b/documentation/parts-list.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Part</t>
   </si>
@@ -76,6 +76,93 @@
   </si>
   <si>
     <t>https://www.ebay.com/itm/318357920728?_skw=2+wire+ntc+temp+sensor&amp;itmmeta=01KY5STM2W67PSQY6X5AEY9STS&amp;hash=item4a1f9c5bd8:g:SG0AAeSw-QdqFCey&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xBwf7Cziw7bL6DzzLsxa2FjQa4JSc3PlZ2kyh%2FLep%2Br1Ylg0h9v811jofOjChe%2FEiO6LX2Bg1BDKDJaW0r0ISx9xFQ8pzlhEnM%2FnYQHJGg2vTzs4zaM2sFiUoiXyJ0lbF3KnRKsO0iD3iDEjsI8xzEBtOOzZmdSs8zSHa%2FYCf1EAT7albnzcpLQabwViqzBnuP4ZYGbnesMKkiuCtUv0ATCE4fePQCMyPNEG3t7qClAv8m8VzButnI8qvMuP4NVoMVqYE0V4kNQ3Aon7ABUUc0OOmXUp5%2BT%2FDgP3E6xZLZkeg%3D%3D%7Ctkp%3ABFBM0sHqufFn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4 inch compression T fitting</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0DXDZKQPD?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_09XT09XKGGNEJC1BXW0M&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_09XT09XKGGNEJC1BXW0M&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2 npt Y fitting</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0DXTMXL95?lv=shuf&amp;psc=1&amp;social_share=cm_sw_r_cso_cp_apin_ct_BPJMEAQA6E2SK7RWG4F5&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_BPJMEAQA6E2SK7RWG4F5&amp;plpRedirect=mhFallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2 inch silicone tubing</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0CPXTZ1MP?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_6JSHERV0HC2CWA22J0P8&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_6JSHERV0HC2CWA22J0P8&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12" Reed valve sending unit</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B08CMJP47D?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_ZBF4SCE0R019KQY09HN8&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_ZBF4SCE0R019KQY09HN8&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12v solenoid valve</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B09P3H56DZ?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_ZP4ND2FJQWX6D43E8CZH&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_ZP4ND2FJQWX6D43E8CZH&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12v power supply</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0DJR3V9DT?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_A0H91Y5TYJ4Q4CT2PXF6&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_A0H91Y5TYJ4Q4CT2PXF6&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infared fire sensor</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0CQ2GWSBZ?lv=shuf&amp;psc=1&amp;social_share=cm_sw_r_cso_cp_apin_ct_02PC961MWHJ3VZFECRH4&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_02PC961MWHJ3VZFECRH4&amp;plpRedirect=mhFallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4 inch compression barb fitting</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0GHJY5XLL?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_3D14H0C81JSBE72FT0Y9&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_3D14H0C81JSBE72FT0Y9&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4 inch copper tubing</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0BLNRX31W?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_V3NWN6F17DW8FBFMZJMM&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_V3NWN6F17DW8FBFMZJMM&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4 inch compression fitting ball valve</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0BP6T35PW?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_SS2NMEW6QFAQBKET8GP4&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_SS2NMEW6QFAQBKET8GP4&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4 inch comression tubing to 1/2 inch NPT</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0CYLKLG7J?lv=shuf&amp;social_share=cm_sw_r_cso_cp_apin_ct_HPT71X428QS515Y0187W&amp;channelId=704&amp;ref_=cm_sw_r_cso_cp_apin_ct_HPT71X428QS515Y0187W&amp;plpRedirect=mhFallback&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thermal paste</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B09VDLH5M6?ref=ppx_yo2ov_dt_b_fed_asin_title&amp;th=1</t>
+  </si>
+  <si>
+    <t>wire</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B073QHZK55?ref=ppx_yo2ov_dt_b_fed_asin_title&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dupont wire crimp kit</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0FJ8LCZ9W?ref=ppx_yo2ov_dt_b_fed_asin_title&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire extinguisher</t>
   </si>
 </sst>
 </file>
@@ -129,14 +216,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -146,14 +227,14 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -173,8 +254,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table2" ref="$A$1:$D$11">
-  <autoFilter ref="$A$1:$D$11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table2" ref="$A$1:$D$25">
+  <autoFilter ref="$A$1:$D$25"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Part"/>
     <tableColumn id="2" name="Link"/>
@@ -673,38 +754,38 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="1">
         <v>322.92000000000002</v>
       </c>
     </row>
     <row r="3" ht="85.5">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1">
@@ -715,10 +796,10 @@
       </c>
     </row>
     <row r="4" ht="185.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1">
@@ -729,10 +810,10 @@
       </c>
     </row>
     <row r="5" ht="171">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="1">
@@ -743,10 +824,10 @@
       </c>
     </row>
     <row r="6" ht="171">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="1">
@@ -757,10 +838,10 @@
       </c>
     </row>
     <row r="7" ht="156.75">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1">
@@ -771,10 +852,10 @@
       </c>
     </row>
     <row r="8" ht="185.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="1">
@@ -785,10 +866,10 @@
       </c>
     </row>
     <row r="9" ht="171">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="1">
@@ -798,98 +879,200 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+    <row r="10" ht="15">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>8.8800000000000008</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>8.9900000000000002</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.9900000000000002</v>
+      </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>28.989999999999998</v>
+      </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1">
+        <v>9.2899999999999991</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>36.990000000000002</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5.9900000000000002</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>14.99</v>
+      </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="A18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>8.5899999999999999</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>8.9900000000000002</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>16.489999999999998</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
+      <c r="A21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
+      <c r="A22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
+      <c r="A23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="B24" s="2"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -2129,6 +2312,90 @@
       <c r="B231" s="2"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
+    </row>
+    <row r="232" ht="14.25">
+      <c r="A232" s="1"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+    </row>
+    <row r="233" ht="14.25">
+      <c r="A233" s="1"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+    </row>
+    <row r="234" ht="14.25">
+      <c r="A234" s="1"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+    </row>
+    <row r="235" ht="14.25">
+      <c r="A235" s="1"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+    </row>
+    <row r="236" ht="14.25">
+      <c r="A236" s="1"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+    </row>
+    <row r="237" ht="14.25">
+      <c r="A237" s="1"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+    </row>
+    <row r="238" ht="14.25">
+      <c r="A238" s="1"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+    </row>
+    <row r="239" ht="14.25">
+      <c r="A239" s="1"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+    </row>
+    <row r="240" ht="14.25">
+      <c r="A240" s="1"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+    </row>
+    <row r="241" ht="14.25">
+      <c r="A241" s="1"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+    </row>
+    <row r="242" ht="14.25">
+      <c r="A242" s="1"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+    </row>
+    <row r="243" ht="14.25">
+      <c r="A243" s="1"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+    </row>
+    <row r="244" ht="14.25">
+      <c r="A244" s="1"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+    </row>
+    <row r="245" ht="14.25">
+      <c r="A245" s="1"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2140,13 +2407,27 @@
     <hyperlink r:id="rId6" ref="B7"/>
     <hyperlink r:id="rId7" ref="B8"/>
     <hyperlink r:id="rId8" ref="B9"/>
+    <hyperlink r:id="rId9" ref="B10"/>
+    <hyperlink r:id="rId10" ref="B11"/>
+    <hyperlink r:id="rId11" ref="B12"/>
+    <hyperlink r:id="rId12" ref="B13"/>
+    <hyperlink r:id="rId13" ref="B14"/>
+    <hyperlink r:id="rId14" ref="B15"/>
+    <hyperlink r:id="rId15" ref="B16"/>
+    <hyperlink r:id="rId16" ref="B17"/>
+    <hyperlink r:id="rId17" ref="B18"/>
+    <hyperlink r:id="rId18" ref="B19"/>
+    <hyperlink r:id="rId19" ref="B20"/>
+    <hyperlink r:id="rId20" ref="B21"/>
+    <hyperlink r:id="rId21" ref="B22"/>
+    <hyperlink r:id="rId22" ref="B23"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId23"/>
   </tableParts>
 </worksheet>
 </file>